--- a/tests/v1/fixtures/office6m/2026-07/bank_statements/HB_HOLD_USD_2026-06.xlsx
+++ b/tests/v1/fixtures/office6m/2026-07/bank_statements/HB_HOLD_USD_2026-06.xlsx
@@ -754,13 +754,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>596959.9</v>
+        <v>723709.9</v>
       </c>
       <c r="E2" t="n">
-        <v>115417.17</v>
+        <v>75417.17</v>
       </c>
       <c r="F2" t="n">
-        <v>712377.0699999999</v>
+        <v>799127.0699999999</v>
       </c>
     </row>
     <row r="3">
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>712377.0699999999</v>
+        <v>799127.0699999999</v>
       </c>
       <c r="E3" t="n">
         <v>500000</v>
       </c>
       <c r="F3" t="n">
-        <v>1212377.07</v>
+        <v>1299127.07</v>
       </c>
     </row>
     <row r="4">
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1212377.07</v>
+        <v>1299127.07</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1212377.07</v>
+        <v>1299127.07</v>
       </c>
     </row>
     <row r="5">
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1212377.07</v>
+        <v>1299127.07</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1212377.07</v>
+        <v>1299127.07</v>
       </c>
     </row>
     <row r="6">
@@ -858,13 +858,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1212377.07</v>
+        <v>1299127.07</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1212377.07</v>
+        <v>1299127.07</v>
       </c>
     </row>
     <row r="7">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1212377.07</v>
+        <v>1299127.07</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1212377.07</v>
+        <v>1299127.07</v>
       </c>
     </row>
     <row r="8">
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1212377.07</v>
+        <v>1299127.07</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1212377.07</v>
+        <v>1299127.07</v>
       </c>
     </row>
     <row r="9">
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1212377.07</v>
+        <v>1299127.07</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1212377.07</v>
+        <v>1299127.07</v>
       </c>
     </row>
     <row r="10">
@@ -962,13 +962,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1212377.07</v>
+        <v>1299127.07</v>
       </c>
       <c r="E10" t="n">
         <v>-38000</v>
       </c>
       <c r="F10" t="n">
-        <v>1174377.07</v>
+        <v>1261127.07</v>
       </c>
     </row>
     <row r="11">
@@ -988,13 +988,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1174377.07</v>
+        <v>1261127.07</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1174377.07</v>
+        <v>1261127.07</v>
       </c>
     </row>
     <row r="12">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1174377.07</v>
+        <v>1261127.07</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1174377.07</v>
+        <v>1261127.07</v>
       </c>
     </row>
     <row r="13">
@@ -1040,13 +1040,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1174377.07</v>
+        <v>1261127.07</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1174377.07</v>
+        <v>1261127.07</v>
       </c>
     </row>
     <row r="14">
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1174377.07</v>
+        <v>1261127.07</v>
       </c>
       <c r="E14" t="n">
         <v>-500000</v>
       </c>
       <c r="F14" t="n">
-        <v>674377.0699999999</v>
+        <v>761127.0699999999</v>
       </c>
     </row>
     <row r="15">
@@ -1092,13 +1092,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>674377.0699999999</v>
+        <v>761127.0699999999</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>674377.0699999999</v>
+        <v>761127.0699999999</v>
       </c>
     </row>
     <row r="16">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>674377.0699999999</v>
+        <v>761127.0699999999</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>674377.0699999999</v>
+        <v>761127.0699999999</v>
       </c>
     </row>
     <row r="17">
@@ -1144,13 +1144,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>674377.0699999999</v>
+        <v>761127.0699999999</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>674377.0699999999</v>
+        <v>761127.0699999999</v>
       </c>
     </row>
     <row r="18">
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>674377.0699999999</v>
+        <v>761127.0699999999</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>674377.0699999999</v>
+        <v>761127.0699999999</v>
       </c>
     </row>
     <row r="19">
@@ -1196,13 +1196,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>674377.0699999999</v>
+        <v>761127.0699999999</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>674377.0699999999</v>
+        <v>761127.0699999999</v>
       </c>
     </row>
     <row r="20">
@@ -1222,13 +1222,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>674377.0699999999</v>
+        <v>761127.0699999999</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>674377.0699999999</v>
+        <v>761127.0699999999</v>
       </c>
     </row>
     <row r="21">
@@ -1248,13 +1248,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>674377.0699999999</v>
+        <v>761127.0699999999</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>674377.0699999999</v>
+        <v>761127.0699999999</v>
       </c>
     </row>
     <row r="22">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>674377.0699999999</v>
+        <v>761127.0699999999</v>
       </c>
       <c r="E22" t="n">
         <v>-40.51</v>
       </c>
       <c r="F22" t="n">
-        <v>674336.5600000001</v>
+        <v>761086.5600000001</v>
       </c>
     </row>
     <row r="23">
@@ -1300,13 +1300,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>674336.5600000001</v>
+        <v>761086.5600000001</v>
       </c>
       <c r="E23" t="n">
         <v>340.21</v>
       </c>
       <c r="F23" t="n">
-        <v>674676.77</v>
+        <v>761426.77</v>
       </c>
     </row>
   </sheetData>
